--- a/reports/jobs_2026-08-28.xlsx
+++ b/reports/jobs_2026-08-28.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3629,17 +3629,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3647,11 +3647,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -3659,12 +3655,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3676,17 +3672,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3694,11 +3690,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -3706,12 +3698,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3723,12 +3715,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3741,11 +3733,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>CO-Colombia-Remote</t>
-        </is>
-      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -3753,12 +3741,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3770,17 +3758,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3796,12 +3784,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3813,17 +3801,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3833,7 +3821,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3843,12 +3831,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3860,17 +3848,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3880,7 +3868,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3890,12 +3878,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3907,12 +3895,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Zscaler India</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3922,12 +3910,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1 - 3 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, IND</t>
+          <t>CO-Colombia-Remote</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3937,12 +3925,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3954,17 +3942,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Data Science Bootcamp with AI</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3980,22 +3968,206 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Zscaler India</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>1 - 3 years</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, IND</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zscaler</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>upGrad</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Data Science Bootcamp with AI</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
           <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I77"/>
+  <autoFilter ref="A1:I81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4073,6 +4245,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4084,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4172,15 +4348,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Tonbo Imaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.tonboimaging.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.tonboimaging.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Vymo</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://getvymo.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4189,38 +4385,58 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Capillary Technologies</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.capillarytech.com/careers/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ather Energy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.atherenergy.com/careers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.capillarytech.com/careers/", waiting until "networkidle"
+  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DeHaat</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://dehaat.com/careers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CONNECTION_CLOSED at https://dehaat.com/careers
+Call log:
+  - navigating to "https://dehaat.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4229,18 +4445,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4249,18 +4465,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4269,18 +4485,38 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4289,38 +4525,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://sharechat.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4329,18 +4545,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4349,18 +4565,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
